--- a/SNGM_Capacitacion_3.8_Operaciones.xlsx
+++ b/SNGM_Capacitacion_3.8_Operaciones.xlsx
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -166,11 +166,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +190,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -555,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66.40000000000001" customWidth="1" min="1" max="1"/>
@@ -804,7 +805,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>CRITERIO DE DIFUSIÓN INFORMATIVA</t>
+          <t>TRABAJADORES AUSENTES CON LICENCIA MÉDICA</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
@@ -813,11 +814,34 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Difusión informativa: para trabajadores que reciben una difusión exclusivamente informativa, pero que no ejecutan, participan ni supervisan la tarea regulada por el documento, se registra la fecha de difusión y "N/A" en evaluación. Esta difusión informativa no modifica la condición de no aplicabilidad definida en la Planilla 1.</t>
+          <t>Los trabajadores que se encuentran con licencia médica figuran en la Hoja 2 con la leyenda "LICENCIA MÉDICA" en amarillo, en lugar de "PENDIENTE" en rojo. Su difusión y evaluación no constituyen incumplimiento: quedan supeditadas a su reincorporación, y así se consignan en la Hoja 3 como fecha comprometida.</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CRITERIO DE DIFUSIÓN INFORMATIVA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Difusión informativa: para trabajadores que reciben una difusión exclusivamente informativa, pero que no ejecutan, participan ni supervisan la tarea regulada por el documento, se registra la fecha de difusión y "N/A" en evaluación. Esta difusión informativa no modifica la condición de no aplicabilidad definida en la Planilla 1.</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1511,9 +1535,9 @@
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="AF7" s="17" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="AF7" s="16" t="inlineStr">
+        <is>
+          <t>25/02/2025</t>
         </is>
       </c>
       <c r="AG7" s="16" t="inlineStr">
@@ -1728,17 +1752,17 @@
           <t>15338787-7</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>ALBERTO REBOLLEDO</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -1908,17 +1932,17 @@
           <t>15612089-8</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>PEDRO LUIS ALVAREZ PEREZ</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -2088,17 +2112,17 @@
           <t>11326446-2</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>ROBERTO ENRIQUE FRITIS ZALAZAR</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -2268,17 +2292,17 @@
           <t>11439946-9</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>HERNAN GUSTAVO DONOSO BORQUEZ</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -2448,17 +2472,17 @@
           <t>16602101-4</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>ALEJANDRO ANDRES HERRERA AGUILERA</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -2628,17 +2652,17 @@
           <t>17606185-5</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>JULIO ELIAS HIDALGO GARCIA</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -2808,17 +2832,17 @@
           <t>20502538-3</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>LISSETTE CONSUELO CALDERÓN GALLARDO</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -2988,17 +3012,17 @@
           <t>18403704-1</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>CRISTIAN OMAR TAPIA LOBOS</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -3168,17 +3192,17 @@
           <t>13515438-5</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>RICARDO KUNZ FLORES</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -3348,17 +3372,17 @@
           <t>15070549-5</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>CRISTOPHER NICOLA SANTIBAÑEZ BAHAMONDES</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -3528,17 +3552,17 @@
           <t>11748137-9</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>ELIAS BALDOMERO BUSTAMANTE ROJAS</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -3708,17 +3732,17 @@
           <t>17302695-1</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>MAURICIO ANDRES BARAHONA CASTILLO</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -3888,17 +3912,17 @@
           <t>15633680-7</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>CRISTOBAL FELIPE DE LA FUENTE CISTERNA</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -4068,17 +4092,17 @@
           <t>11724812-7</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>CRISTIAN HOMERO DIAZ VEGA</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -4248,17 +4272,17 @@
           <t>19352719-1</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>MATIAS IGNACIO FUENTES FUENTES</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -4428,17 +4452,17 @@
           <t>16821701-3</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>VICTOR ALEJANDRO JOFRE DELGADO</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -4608,17 +4632,17 @@
           <t>17302213-1</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>MARCO ANDRE OVIEDO FERNANDEZ</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -4788,17 +4812,17 @@
           <t>15913813-5</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>JOSE ROBERTO VALDES ROJAS</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -4968,17 +4992,17 @@
           <t>15014074-9</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>MIGUEL ANGEL MARTINEZ VEGA</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -5148,17 +5172,17 @@
           <t>18211987-3</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>OSVALDO IGNACIO MUÑOZ BARRIA</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -5328,17 +5352,17 @@
           <t>14114592-4</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>JUAN ALEJANDRO IBACETA GARCIA</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -5508,17 +5532,17 @@
           <t>15033441-1</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>DARIO ANTONIO CASTILLO OLGUIN</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -5688,17 +5712,17 @@
           <t>19124925-9</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>LUIS FELIPE CISTERNAS AGUIRRE</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -5868,17 +5892,17 @@
           <t>17294689-5</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>RODRIGO EDUARDO COLLAO LABARCA</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -6048,17 +6072,17 @@
           <t>12444781-K</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>ROBERTO MAURICIO ESCOBAR RUBINA</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -6228,17 +6252,17 @@
           <t>14151103-3</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>JORGE ANGELO VEGA HERRERA</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -6408,17 +6432,17 @@
           <t>21870635-5</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>RODRIGO DAZA BERTICHEVIC</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Operador Base</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -6583,22 +6607,22 @@
       <c r="A36" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>LEONARDO SAAVEDRA</t>
         </is>
       </c>
-      <c r="D36" s="18" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -6768,17 +6792,17 @@
           <t>15870483-8</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>JAMES JHON JAN-SIN BOWN HERRERA</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -6948,17 +6972,17 @@
           <t>13358835-3</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>OSVALDO ARTURO GALLEGUILLOS ARAYA</t>
         </is>
       </c>
-      <c r="D38" s="18" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -7128,17 +7152,17 @@
           <t>18138905-2</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>ALEX NICOLAS BARAHONA CASTILLO</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -7308,17 +7332,17 @@
           <t>15031548-4</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>JULIO ANDRES BARLARO PODETTI</t>
         </is>
       </c>
-      <c r="D40" s="18" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -7488,17 +7512,17 @@
           <t>17902171-4</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>FERNANDO ILDEFONSO VARGAS ROMO</t>
         </is>
       </c>
-      <c r="D41" s="18" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -7668,17 +7692,17 @@
           <t>18399063-2</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>JEAN MARIO CARVAJAL SALINAS</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -7848,17 +7872,17 @@
           <t>18845157-8</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>ESTEBAN GERMAN TAPIA LOBOS</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -8023,22 +8047,22 @@
       <c r="A44" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>19353026-5</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>GABRIELA VARAS</t>
         </is>
       </c>
-      <c r="D44" s="18" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>Operador Base</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -9054,12 +9078,12 @@
         </is>
       </c>
       <c r="BE8" s="21" t="n"/>
-      <c r="BF8" s="17" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="BG8" s="20" t="n"/>
+      <c r="BF8" s="16" t="inlineStr">
+        <is>
+          <t>25/02/2025</t>
+        </is>
+      </c>
+      <c r="BG8" s="21" t="n"/>
       <c r="BH8" s="16" t="inlineStr">
         <is>
           <t>14/07/2026</t>
@@ -9625,17 +9649,17 @@
           <t>15338787-7</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>ALBERTO REBOLLEDO</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -9960,17 +9984,17 @@
           <t>15612089-8</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>PEDRO LUIS ALVAREZ PEREZ</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -10295,17 +10319,17 @@
           <t>11326446-2</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>ROBERTO ENRIQUE FRITIS ZALAZAR</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -10630,17 +10654,17 @@
           <t>11439946-9</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>HERNAN GUSTAVO DONOSO BORQUEZ</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -10965,17 +10989,17 @@
           <t>16602101-4</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>ALEJANDRO ANDRES HERRERA AGUILERA</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -11300,17 +11324,17 @@
           <t>17606185-5</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>JULIO ELIAS HIDALGO GARCIA</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -11635,17 +11659,17 @@
           <t>20502538-3</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>LISSETTE CONSUELO CALDERÓN GALLARDO</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -11970,17 +11994,17 @@
           <t>18403704-1</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>CRISTIAN OMAR TAPIA LOBOS</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -12305,17 +12329,17 @@
           <t>13515438-5</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>RICARDO KUNZ FLORES</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -12640,329 +12664,329 @@
           <t>15070549-5</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>CRISTOPHER NICOLA SANTIBAÑEZ BAHAMONDES</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="L20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="M20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="N20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="O20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="P20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="Q20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="R20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="S20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="T20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="U20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="V20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="W20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="X20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="Y20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="Z20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AA20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AB20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AC20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AD20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AE20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AF20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AG20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AH20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AI20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AJ20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AK20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AL20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AM20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AN20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AO20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AP20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AQ20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AR20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AS20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AT20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AU20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AV20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AW20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AX20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AY20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AZ20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BA20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BB20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BC20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BD20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BE20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BF20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BG20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BH20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BI20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BK20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BL20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BM20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BN20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BO20" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="N20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="O20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="P20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="Q20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="R20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="S20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="T20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="U20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="V20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="W20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="X20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="Y20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="Z20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AA20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AB20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AC20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AD20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AE20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AF20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AG20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AH20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AI20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AJ20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AK20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AL20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AM20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AN20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AO20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AP20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AQ20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AR20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AS20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AT20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AU20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AV20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AW20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AX20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AY20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AZ20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BA20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BB20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BC20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BD20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BE20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BF20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BG20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BH20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BI20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BJ20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BK20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BL20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BM20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BN20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BO20" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
         </is>
       </c>
     </row>
@@ -12975,17 +12999,17 @@
           <t>11748137-9</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>ELIAS BALDOMERO BUSTAMANTE ROJAS</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -13310,17 +13334,17 @@
           <t>17302695-1</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>MAURICIO ANDRES BARAHONA CASTILLO</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -13645,17 +13669,17 @@
           <t>15633680-7</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>CRISTOBAL FELIPE DE LA FUENTE CISTERNA</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -13980,17 +14004,17 @@
           <t>11724812-7</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>CRISTIAN HOMERO DIAZ VEGA</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -14315,17 +14339,17 @@
           <t>19352719-1</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>MATIAS IGNACIO FUENTES FUENTES</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -14650,17 +14674,17 @@
           <t>16821701-3</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>VICTOR ALEJANDRO JOFRE DELGADO</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -14985,17 +15009,17 @@
           <t>17302213-1</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>MARCO ANDRE OVIEDO FERNANDEZ</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -15320,17 +15344,17 @@
           <t>15913813-5</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>JOSE ROBERTO VALDES ROJAS</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -15655,17 +15679,17 @@
           <t>15014074-9</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>MIGUEL ANGEL MARTINEZ VEGA</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -15990,17 +16014,17 @@
           <t>18211987-3</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>OSVALDO IGNACIO MUÑOZ BARRIA</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -16325,17 +16349,17 @@
           <t>14114592-4</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>JUAN ALEJANDRO IBACETA GARCIA</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -16660,17 +16684,17 @@
           <t>15033441-1</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>DARIO ANTONIO CASTILLO OLGUIN</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -16995,17 +17019,17 @@
           <t>19124925-9</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>LUIS FELIPE CISTERNAS AGUIRRE</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -17330,17 +17354,17 @@
           <t>17294689-5</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>RODRIGO EDUARDO COLLAO LABARCA</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -17665,17 +17689,17 @@
           <t>12444781-K</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>ROBERTO MAURICIO ESCOBAR RUBINA</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -18000,17 +18024,17 @@
           <t>14151103-3</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>JORGE ANGELO VEGA HERRERA</t>
         </is>
       </c>
-      <c r="D36" s="18" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -18335,17 +18359,17 @@
           <t>21870635-5</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>RODRIGO DAZA BERTICHEVIC</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Operador Base</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -18665,334 +18689,334 @@
       <c r="A38" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>LEONARDO SAAVEDRA</t>
         </is>
       </c>
-      <c r="D38" s="18" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="H38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="I38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="L38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="M38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="N38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="O38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="P38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="Q38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="R38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="S38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="T38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="U38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="V38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="W38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="X38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="Y38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="Z38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AA38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AB38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AC38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AD38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AE38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AF38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AG38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AH38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AI38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AJ38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AK38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AL38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AM38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AN38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AO38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AP38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AQ38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AR38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AS38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AT38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AU38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AV38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AW38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AX38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AY38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="AZ38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BA38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BB38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BC38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BD38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BE38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BF38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BG38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BH38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BI38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BJ38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BK38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BL38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BM38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BN38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="BO38" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="K38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="L38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="M38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="N38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="O38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="P38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="Q38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="R38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="S38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="T38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="U38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="V38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="W38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="X38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="Y38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="Z38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AA38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AB38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AC38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AD38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AE38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AF38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AG38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AH38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AI38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AJ38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AK38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AL38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AM38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AN38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AO38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AP38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AQ38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AR38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AS38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AT38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AU38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AV38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AW38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AX38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AY38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="AZ38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BA38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BB38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BC38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BD38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BE38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BF38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BG38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BH38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BI38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BJ38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BK38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BL38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BM38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BN38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
+        </is>
+      </c>
+      <c r="BO38" s="18" t="inlineStr">
+        <is>
+          <t>LICENCIA MÉDICA</t>
         </is>
       </c>
     </row>
@@ -19005,17 +19029,17 @@
           <t>15870483-8</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>JAMES JHON JAN-SIN BOWN HERRERA</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -19340,17 +19364,17 @@
           <t>13358835-3</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>OSVALDO ARTURO GALLEGUILLOS ARAYA</t>
         </is>
       </c>
-      <c r="D40" s="18" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -19675,17 +19699,17 @@
           <t>18138905-2</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>ALEX NICOLAS BARAHONA CASTILLO</t>
         </is>
       </c>
-      <c r="D41" s="18" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -20010,17 +20034,17 @@
           <t>15031548-4</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>JULIO ANDRES BARLARO PODETTI</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -20345,17 +20369,17 @@
           <t>17902171-4</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>FERNANDO ILDEFONSO VARGAS ROMO</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -20680,17 +20704,17 @@
           <t>18399063-2</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>JEAN MARIO CARVAJAL SALINAS</t>
         </is>
       </c>
-      <c r="D44" s="18" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -21015,17 +21039,17 @@
           <t>18845157-8</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>ESTEBAN GERMAN TAPIA LOBOS</t>
         </is>
       </c>
-      <c r="D45" s="18" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E45" s="18" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -21345,22 +21369,22 @@
       <c r="A46" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>19353026-5</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>GABRIELA VARAS</t>
         </is>
       </c>
-      <c r="D46" s="18" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Operador Base</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -21849,7 +21873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21951,17 +21975,17 @@
           <t>15338787-7</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ALBERTO REBOLLEDO</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -21976,12 +22000,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22011,17 +22035,17 @@
           <t>15612089-8</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>PEDRO LUIS ALVAREZ PEREZ</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22036,12 +22060,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22071,17 +22095,17 @@
           <t>11326446-2</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>ROBERTO ENRIQUE FRITIS ZALAZAR</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22096,12 +22120,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22131,17 +22155,17 @@
           <t>11439946-9</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>HERNAN GUSTAVO DONOSO BORQUEZ</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22156,12 +22180,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22191,17 +22215,17 @@
           <t>16602101-4</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>ALEJANDRO ANDRES HERRERA AGUILERA</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22216,12 +22240,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22251,17 +22275,17 @@
           <t>17606185-5</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>JULIO ELIAS HIDALGO GARCIA</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22276,12 +22300,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22311,17 +22335,17 @@
           <t>20502538-3</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>LISSETTE CONSUELO CALDERÓN GALLARDO</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22336,12 +22360,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22371,17 +22395,17 @@
           <t>18403704-1</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>CRISTIAN OMAR TAPIA LOBOS</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22396,12 +22420,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22431,17 +22455,17 @@
           <t>13515438-5</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>RICARDO KUNZ FLORES</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22456,12 +22480,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22491,17 +22515,17 @@
           <t>15070549-5</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>CRISTOPHER NICOLA SANTIBAÑEZ BAHAMONDES</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22516,24 +22540,24 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>A su reincorporación (licencia médica)</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>A su reincorporación (licencia médica)</t>
         </is>
       </c>
       <c r="L14" s="25" t="inlineStr">
@@ -22551,17 +22575,17 @@
           <t>11748137-9</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>ELIAS BALDOMERO BUSTAMANTE ROJAS</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22576,12 +22600,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22611,17 +22635,17 @@
           <t>17302695-1</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>MAURICIO ANDRES BARAHONA CASTILLO</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22636,12 +22660,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22671,17 +22695,17 @@
           <t>15633680-7</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>CRISTOBAL FELIPE DE LA FUENTE CISTERNA</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22696,12 +22720,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22731,17 +22755,17 @@
           <t>11724812-7</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>CRISTIAN HOMERO DIAZ VEGA</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22756,12 +22780,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22791,17 +22815,17 @@
           <t>19352719-1</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>MATIAS IGNACIO FUENTES FUENTES</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22816,12 +22840,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22851,17 +22875,17 @@
           <t>16821701-3</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>VICTOR ALEJANDRO JOFRE DELGADO</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22876,12 +22900,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22911,17 +22935,17 @@
           <t>17302213-1</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>MARCO ANDRE OVIEDO FERNANDEZ</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22936,12 +22960,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22971,17 +22995,17 @@
           <t>15913813-5</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>JOSE ROBERTO VALDES ROJAS</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -22996,12 +23020,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23031,17 +23055,17 @@
           <t>15014074-9</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>MIGUEL ANGEL MARTINEZ VEGA</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23056,12 +23080,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H23" s="18" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23091,17 +23115,17 @@
           <t>18211987-3</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>OSVALDO IGNACIO MUÑOZ BARRIA</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23116,12 +23140,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23151,17 +23175,17 @@
           <t>14114592-4</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>JUAN ALEJANDRO IBACETA GARCIA</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23176,12 +23200,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23211,17 +23235,17 @@
           <t>15033441-1</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>DARIO ANTONIO CASTILLO OLGUIN</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23236,12 +23260,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23271,17 +23295,17 @@
           <t>19124925-9</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>LUIS FELIPE CISTERNAS AGUIRRE</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23296,12 +23320,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H27" s="18" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23331,17 +23355,17 @@
           <t>17294689-5</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>RODRIGO EDUARDO COLLAO LABARCA</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23356,12 +23380,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23391,17 +23415,17 @@
           <t>12444781-K</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>ROBERTO MAURICIO ESCOBAR RUBINA</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23416,12 +23440,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H29" s="18" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23451,17 +23475,17 @@
           <t>14151103-3</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>JORGE ANGELO VEGA HERRERA</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23476,12 +23500,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H30" s="18" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23511,17 +23535,17 @@
           <t>21870635-5</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>RODRIGO DAZA BERTICHEVIC</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Operador Base</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23536,12 +23560,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H31" s="18" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23566,22 +23590,22 @@
       <c r="A32" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>LEONARDO SAAVEDRA</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23596,24 +23620,24 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K32" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
+      <c r="J32" s="18" t="inlineStr">
+        <is>
+          <t>A su reincorporación (licencia médica)</t>
+        </is>
+      </c>
+      <c r="K32" s="18" t="inlineStr">
+        <is>
+          <t>A su reincorporación (licencia médica)</t>
         </is>
       </c>
       <c r="L32" s="25" t="inlineStr">
@@ -23631,17 +23655,17 @@
           <t>15870483-8</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>JAMES JHON JAN-SIN BOWN HERRERA</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23656,12 +23680,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H33" s="18" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23691,17 +23715,17 @@
           <t>13358835-3</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>OSVALDO ARTURO GALLEGUILLOS ARAYA</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23716,12 +23740,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H34" s="18" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23751,17 +23775,17 @@
           <t>18138905-2</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>ALEX NICOLAS BARAHONA CASTILLO</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23776,12 +23800,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23811,17 +23835,17 @@
           <t>15031548-4</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>JULIO ANDRES BARLARO PODETTI</t>
         </is>
       </c>
-      <c r="D36" s="18" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23836,12 +23860,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23871,17 +23895,17 @@
           <t>17902171-4</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>FERNANDO ILDEFONSO VARGAS ROMO</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23896,12 +23920,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H37" s="18" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23931,17 +23955,17 @@
           <t>18399063-2</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>JEAN MARIO CARVAJAL SALINAS</t>
         </is>
       </c>
-      <c r="D38" s="18" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -23956,12 +23980,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H38" s="18" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I38" s="17" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23991,17 +24015,17 @@
           <t>18845157-8</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>ESTEBAN GERMAN TAPIA LOBOS</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24016,12 +24040,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H39" s="18" t="inlineStr">
+      <c r="H39" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I39" s="17" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24046,22 +24070,22 @@
       <c r="A40" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>19353026-5</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>GABRIELA VARAS</t>
         </is>
       </c>
-      <c r="D40" s="18" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Operador Base</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24076,12 +24100,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H40" s="18" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>Plan de Gestión de Riesgos de Desastres</t>
         </is>
       </c>
-      <c r="I40" s="17" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24111,17 +24135,17 @@
           <t>15338787-7</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>ALBERTO REBOLLEDO</t>
         </is>
       </c>
-      <c r="D41" s="18" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24136,12 +24160,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H41" s="18" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I41" s="17" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24171,17 +24195,17 @@
           <t>15612089-8</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>PEDRO LUIS ALVAREZ PEREZ</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24196,12 +24220,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H42" s="18" t="inlineStr">
+      <c r="H42" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24231,17 +24255,17 @@
           <t>11326446-2</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>ROBERTO ENRIQUE FRITIS ZALAZAR</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24256,12 +24280,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H43" s="18" t="inlineStr">
+      <c r="H43" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24291,17 +24315,17 @@
           <t>11439946-9</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>HERNAN GUSTAVO DONOSO BORQUEZ</t>
         </is>
       </c>
-      <c r="D44" s="18" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24316,12 +24340,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H44" s="18" t="inlineStr">
+      <c r="H44" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I44" s="17" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24351,17 +24375,17 @@
           <t>16602101-4</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>ALEJANDRO ANDRES HERRERA AGUILERA</t>
         </is>
       </c>
-      <c r="D45" s="18" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E45" s="18" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24376,12 +24400,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H45" s="18" t="inlineStr">
+      <c r="H45" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I45" s="17" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24411,17 +24435,17 @@
           <t>17606185-5</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>JULIO ELIAS HIDALGO GARCIA</t>
         </is>
       </c>
-      <c r="D46" s="18" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24436,12 +24460,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H46" s="18" t="inlineStr">
+      <c r="H46" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I46" s="17" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24471,17 +24495,17 @@
           <t>20502538-3</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>LISSETTE CONSUELO CALDERÓN GALLARDO</t>
         </is>
       </c>
-      <c r="D47" s="18" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E47" s="18" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24496,12 +24520,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H47" s="18" t="inlineStr">
+      <c r="H47" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I47" s="17" t="inlineStr">
+      <c r="I47" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24531,17 +24555,17 @@
           <t>18403704-1</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>CRISTIAN OMAR TAPIA LOBOS</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24556,12 +24580,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H48" s="18" t="inlineStr">
+      <c r="H48" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I48" s="17" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24591,17 +24615,17 @@
           <t>13515438-5</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>RICARDO KUNZ FLORES</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24616,12 +24640,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H49" s="18" t="inlineStr">
+      <c r="H49" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24651,17 +24675,17 @@
           <t>15070549-5</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>CRISTOPHER NICOLA SANTIBAÑEZ BAHAMONDES</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24676,24 +24700,24 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H50" s="18" t="inlineStr">
+      <c r="H50" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I50" s="17" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K50" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
+      <c r="J50" s="18" t="inlineStr">
+        <is>
+          <t>A su reincorporación (licencia médica)</t>
+        </is>
+      </c>
+      <c r="K50" s="18" t="inlineStr">
+        <is>
+          <t>A su reincorporación (licencia médica)</t>
         </is>
       </c>
       <c r="L50" s="25" t="inlineStr">
@@ -24711,17 +24735,17 @@
           <t>11748137-9</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="17" t="inlineStr">
         <is>
           <t>ELIAS BALDOMERO BUSTAMANTE ROJAS</t>
         </is>
       </c>
-      <c r="D51" s="18" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24736,12 +24760,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H51" s="18" t="inlineStr">
+      <c r="H51" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I51" s="17" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24771,17 +24795,17 @@
           <t>17302695-1</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>MAURICIO ANDRES BARAHONA CASTILLO</t>
         </is>
       </c>
-      <c r="D52" s="18" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24796,12 +24820,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H52" s="18" t="inlineStr">
+      <c r="H52" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I52" s="17" t="inlineStr">
+      <c r="I52" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24831,17 +24855,17 @@
           <t>15633680-7</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>CRISTOBAL FELIPE DE LA FUENTE CISTERNA</t>
         </is>
       </c>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E53" s="18" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24856,12 +24880,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H53" s="18" t="inlineStr">
+      <c r="H53" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I53" s="17" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24891,17 +24915,17 @@
           <t>11724812-7</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>CRISTIAN HOMERO DIAZ VEGA</t>
         </is>
       </c>
-      <c r="D54" s="18" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24916,12 +24940,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H54" s="18" t="inlineStr">
+      <c r="H54" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I54" s="17" t="inlineStr">
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24951,17 +24975,17 @@
           <t>19352719-1</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>MATIAS IGNACIO FUENTES FUENTES</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -24976,12 +25000,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H55" s="18" t="inlineStr">
+      <c r="H55" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I55" s="17" t="inlineStr">
+      <c r="I55" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25011,17 +25035,17 @@
           <t>16821701-3</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>VICTOR ALEJANDRO JOFRE DELGADO</t>
         </is>
       </c>
-      <c r="D56" s="18" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E56" s="18" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25036,12 +25060,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H56" s="18" t="inlineStr">
+      <c r="H56" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I56" s="17" t="inlineStr">
+      <c r="I56" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25071,17 +25095,17 @@
           <t>17302213-1</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>MARCO ANDRE OVIEDO FERNANDEZ</t>
         </is>
       </c>
-      <c r="D57" s="18" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25096,12 +25120,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="H57" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I57" s="17" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25131,17 +25155,17 @@
           <t>15913813-5</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C58" s="17" t="inlineStr">
         <is>
           <t>JOSE ROBERTO VALDES ROJAS</t>
         </is>
       </c>
-      <c r="D58" s="18" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E58" s="18" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25156,12 +25180,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H58" s="18" t="inlineStr">
+      <c r="H58" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I58" s="17" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25191,17 +25215,17 @@
           <t>15014074-9</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>MIGUEL ANGEL MARTINEZ VEGA</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25216,12 +25240,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="H59" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I59" s="17" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25251,17 +25275,17 @@
           <t>18211987-3</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>OSVALDO IGNACIO MUÑOZ BARRIA</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25276,12 +25300,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="H60" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I60" s="17" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25311,17 +25335,17 @@
           <t>14114592-4</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="17" t="inlineStr">
         <is>
           <t>JUAN ALEJANDRO IBACETA GARCIA</t>
         </is>
       </c>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E61" s="18" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25336,12 +25360,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H61" s="18" t="inlineStr">
+      <c r="H61" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I61" s="17" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25371,17 +25395,17 @@
           <t>15033441-1</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>DARIO ANTONIO CASTILLO OLGUIN</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E62" s="18" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25396,12 +25420,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H62" s="18" t="inlineStr">
+      <c r="H62" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I62" s="17" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25431,17 +25455,17 @@
           <t>19124925-9</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>LUIS FELIPE CISTERNAS AGUIRRE</t>
         </is>
       </c>
-      <c r="D63" s="18" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E63" s="18" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25456,12 +25480,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H63" s="18" t="inlineStr">
+      <c r="H63" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I63" s="17" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25491,17 +25515,17 @@
           <t>17294689-5</t>
         </is>
       </c>
-      <c r="C64" s="18" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>RODRIGO EDUARDO COLLAO LABARCA</t>
         </is>
       </c>
-      <c r="D64" s="18" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E64" s="18" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25516,12 +25540,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H64" s="18" t="inlineStr">
+      <c r="H64" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I64" s="17" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25551,17 +25575,17 @@
           <t>12444781-K</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <t>ROBERTO MAURICIO ESCOBAR RUBINA</t>
         </is>
       </c>
-      <c r="D65" s="18" t="inlineStr">
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E65" s="18" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25576,12 +25600,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H65" s="18" t="inlineStr">
+      <c r="H65" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I65" s="17" t="inlineStr">
+      <c r="I65" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25611,17 +25635,17 @@
           <t>14151103-3</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr">
+      <c r="C66" s="17" t="inlineStr">
         <is>
           <t>JORGE ANGELO VEGA HERRERA</t>
         </is>
       </c>
-      <c r="D66" s="18" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E66" s="18" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25636,12 +25660,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="H66" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I66" s="17" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25671,17 +25695,17 @@
           <t>21870635-5</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="17" t="inlineStr">
         <is>
           <t>RODRIGO DAZA BERTICHEVIC</t>
         </is>
       </c>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>Operador Base</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25696,12 +25720,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="H67" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I67" s="17" t="inlineStr">
+      <c r="I67" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25726,22 +25750,22 @@
       <c r="A68" s="16" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <t>LEONARDO SAAVEDRA</t>
         </is>
       </c>
-      <c r="D68" s="18" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>Supervisor de Operaciones</t>
         </is>
       </c>
-      <c r="E68" s="18" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25756,24 +25780,24 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H68" s="18" t="inlineStr">
+      <c r="H68" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I68" s="17" t="inlineStr">
+      <c r="I68" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
-      <c r="J68" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K68" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
+      <c r="J68" s="18" t="inlineStr">
+        <is>
+          <t>A su reincorporación (licencia médica)</t>
+        </is>
+      </c>
+      <c r="K68" s="18" t="inlineStr">
+        <is>
+          <t>A su reincorporación (licencia médica)</t>
         </is>
       </c>
       <c r="L68" s="25" t="inlineStr">
@@ -25791,17 +25815,17 @@
           <t>15870483-8</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>JAMES JHON JAN-SIN BOWN HERRERA</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Controlador Operación Puerto</t>
         </is>
       </c>
-      <c r="E69" s="18" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25816,12 +25840,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H69" s="18" t="inlineStr">
+      <c r="H69" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I69" s="17" t="inlineStr">
+      <c r="I69" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25851,17 +25875,17 @@
           <t>13358835-3</t>
         </is>
       </c>
-      <c r="C70" s="18" t="inlineStr">
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <t>OSVALDO ARTURO GALLEGUILLOS ARAYA</t>
         </is>
       </c>
-      <c r="D70" s="18" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>Operador Líder Puerto</t>
         </is>
       </c>
-      <c r="E70" s="18" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25876,12 +25900,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H70" s="18" t="inlineStr">
+      <c r="H70" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I70" s="17" t="inlineStr">
+      <c r="I70" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25911,17 +25935,17 @@
           <t>18138905-2</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
+      <c r="C71" s="17" t="inlineStr">
         <is>
           <t>ALEX NICOLAS BARAHONA CASTILLO</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E71" s="18" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25936,12 +25960,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H71" s="18" t="inlineStr">
+      <c r="H71" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I71" s="17" t="inlineStr">
+      <c r="I71" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -25971,17 +25995,17 @@
           <t>15031548-4</t>
         </is>
       </c>
-      <c r="C72" s="18" t="inlineStr">
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <t>JULIO ANDRES BARLARO PODETTI</t>
         </is>
       </c>
-      <c r="D72" s="18" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E72" s="18" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -25996,12 +26020,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H72" s="18" t="inlineStr">
+      <c r="H72" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I72" s="17" t="inlineStr">
+      <c r="I72" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -26031,17 +26055,17 @@
           <t>17902171-4</t>
         </is>
       </c>
-      <c r="C73" s="18" t="inlineStr">
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>FERNANDO ILDEFONSO VARGAS ROMO</t>
         </is>
       </c>
-      <c r="D73" s="18" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
         <is>
           <t>Operador Especialista Puerto</t>
         </is>
       </c>
-      <c r="E73" s="18" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -26056,12 +26080,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H73" s="18" t="inlineStr">
+      <c r="H73" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I73" s="17" t="inlineStr">
+      <c r="I73" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -26091,17 +26115,17 @@
           <t>18399063-2</t>
         </is>
       </c>
-      <c r="C74" s="18" t="inlineStr">
+      <c r="C74" s="17" t="inlineStr">
         <is>
           <t>JEAN MARIO CARVAJAL SALINAS</t>
         </is>
       </c>
-      <c r="D74" s="18" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -26116,12 +26140,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H74" s="18" t="inlineStr">
+      <c r="H74" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I74" s="17" t="inlineStr">
+      <c r="I74" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -26151,17 +26175,17 @@
           <t>18845157-8</t>
         </is>
       </c>
-      <c r="C75" s="18" t="inlineStr">
+      <c r="C75" s="17" t="inlineStr">
         <is>
           <t>ESTEBAN GERMAN TAPIA LOBOS</t>
         </is>
       </c>
-      <c r="D75" s="18" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
         <is>
           <t>Operador Avanzado Puerto</t>
         </is>
       </c>
-      <c r="E75" s="18" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -26176,12 +26200,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H75" s="18" t="inlineStr">
+      <c r="H75" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I75" s="17" t="inlineStr">
+      <c r="I75" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -26206,22 +26230,22 @@
       <c r="A76" s="16" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>19353026-5</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>GABRIELA VARAS</t>
         </is>
       </c>
-      <c r="D76" s="18" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>Operador Base</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
@@ -26236,12 +26260,12 @@
           <t>Difusión y Evaluación</t>
         </is>
       </c>
-      <c r="H76" s="18" t="inlineStr">
+      <c r="H76" s="17" t="inlineStr">
         <is>
           <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
-      <c r="I76" s="17" t="inlineStr">
+      <c r="I76" s="18" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -26300,14 +26324,21 @@
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>Los trabajadores Leonardo Saavedra y Gabriela Varas figuran con RUT POR CONFIRMAR: no aparecen en el listado de RUT recibido.</t>
+          <t>Los trabajadores con licencia médica llevan como fecha comprometida "A su reincorporación": CRISTOPHER NICOLA SANTIBAÑEZ BAHAMONDES, LEONARDO SAAVEDRA.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>Documento 3.8.3.12 "Procedimiento de Emergencia": su fecha de aprobación quedó POR CONFIRMAR, por no figurar en el repositorio documental consultado.</t>
+          <t>Documento 3.8.3.12 "Procedimiento de Emergencia": corresponde al "Plan de Respuesta a Emergencia Local Valle Copiapó — Puerto Punta Totoralillo", aprobado el 25/02/2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>Trabajadores con RUT POR CONFIRMAR: LEONARDO SAAVEDRA.</t>
         </is>
       </c>
     </row>

--- a/SNGM_Capacitacion_3.8_Operaciones.xlsx
+++ b/SNGM_Capacitacion_3.8_Operaciones.xlsx
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -176,9 +176,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -758,7 +755,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Realizado y con registro documental disponible (difusión efectuada o evaluación rendida y aprobada). Se utiliza sólo en las Hojas 2 y 3.</t>
+          <t>Realizado y con registro documental disponible (difusión efectuada o evaluación rendida y aprobada), o bien situación regularizada sin observaciones, como la de los trabajadores ausentes con licencia médica, identificados en la propia celda. Se utiliza sólo en las Hojas 2 y 3.</t>
         </is>
       </c>
     </row>
@@ -12499,9 +12496,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AK19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AK19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AL19" s="22" t="inlineStr">
@@ -12509,9 +12506,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AM19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AM19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AN19" s="22" t="inlineStr">
@@ -12519,9 +12516,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AO19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AO19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AP19" s="22" t="inlineStr">
@@ -12529,9 +12526,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AQ19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AQ19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AR19" s="22" t="inlineStr">
@@ -12539,9 +12536,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AS19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AS19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AT19" s="22" t="inlineStr">
@@ -12549,9 +12546,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AU19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AU19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AV19" s="22" t="inlineStr">
@@ -12559,9 +12556,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AW19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AW19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AX19" s="22" t="inlineStr">
@@ -12569,9 +12566,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AY19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AY19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AZ19" s="22" t="inlineStr">
@@ -12579,9 +12576,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB19" s="22" t="inlineStr">
@@ -12589,9 +12586,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD19" s="22" t="inlineStr">
@@ -12599,9 +12596,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF19" s="22" t="inlineStr">
@@ -12609,9 +12606,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH19" s="22" t="inlineStr">
@@ -12619,9 +12616,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ19" s="22" t="inlineStr">
@@ -12629,9 +12626,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL19" s="22" t="inlineStr">
@@ -12639,9 +12636,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN19" s="22" t="inlineStr">
@@ -12649,9 +12646,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO19" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO19" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -12679,312 +12676,312 @@
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="K20" s="18" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="L20" s="18" t="inlineStr">
+      <c r="L20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="M20" s="18" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="N20" s="18" t="inlineStr">
+      <c r="N20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="O20" s="18" t="inlineStr">
+      <c r="O20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="P20" s="18" t="inlineStr">
+      <c r="P20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="Q20" s="18" t="inlineStr">
+      <c r="Q20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="R20" s="18" t="inlineStr">
+      <c r="R20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="S20" s="18" t="inlineStr">
+      <c r="S20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="T20" s="18" t="inlineStr">
+      <c r="T20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="U20" s="18" t="inlineStr">
+      <c r="U20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="V20" s="18" t="inlineStr">
+      <c r="V20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="W20" s="18" t="inlineStr">
+      <c r="W20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="X20" s="18" t="inlineStr">
+      <c r="X20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="Y20" s="18" t="inlineStr">
+      <c r="Y20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="Z20" s="18" t="inlineStr">
+      <c r="Z20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AA20" s="18" t="inlineStr">
+      <c r="AA20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AB20" s="18" t="inlineStr">
+      <c r="AB20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AC20" s="18" t="inlineStr">
+      <c r="AC20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AD20" s="18" t="inlineStr">
+      <c r="AD20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AE20" s="18" t="inlineStr">
+      <c r="AE20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AF20" s="18" t="inlineStr">
+      <c r="AF20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AG20" s="18" t="inlineStr">
+      <c r="AG20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AH20" s="18" t="inlineStr">
+      <c r="AH20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AI20" s="18" t="inlineStr">
+      <c r="AI20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AJ20" s="18" t="inlineStr">
+      <c r="AJ20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AK20" s="18" t="inlineStr">
+      <c r="AK20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AL20" s="18" t="inlineStr">
+      <c r="AL20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AM20" s="18" t="inlineStr">
+      <c r="AM20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AN20" s="18" t="inlineStr">
+      <c r="AN20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AO20" s="18" t="inlineStr">
+      <c r="AO20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AP20" s="18" t="inlineStr">
+      <c r="AP20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AQ20" s="18" t="inlineStr">
+      <c r="AQ20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AR20" s="18" t="inlineStr">
+      <c r="AR20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AS20" s="18" t="inlineStr">
+      <c r="AS20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AT20" s="18" t="inlineStr">
+      <c r="AT20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AU20" s="18" t="inlineStr">
+      <c r="AU20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AV20" s="18" t="inlineStr">
+      <c r="AV20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AW20" s="18" t="inlineStr">
+      <c r="AW20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AX20" s="18" t="inlineStr">
+      <c r="AX20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AY20" s="18" t="inlineStr">
+      <c r="AY20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AZ20" s="18" t="inlineStr">
+      <c r="AZ20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BA20" s="18" t="inlineStr">
+      <c r="BA20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BB20" s="18" t="inlineStr">
+      <c r="BB20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BC20" s="18" t="inlineStr">
+      <c r="BC20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BD20" s="18" t="inlineStr">
+      <c r="BD20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BE20" s="18" t="inlineStr">
+      <c r="BE20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BF20" s="18" t="inlineStr">
+      <c r="BF20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BG20" s="18" t="inlineStr">
+      <c r="BG20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BH20" s="18" t="inlineStr">
+      <c r="BH20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BI20" s="18" t="inlineStr">
+      <c r="BI20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BJ20" s="18" t="inlineStr">
+      <c r="BJ20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BK20" s="18" t="inlineStr">
+      <c r="BK20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BL20" s="18" t="inlineStr">
+      <c r="BL20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BM20" s="18" t="inlineStr">
+      <c r="BM20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BN20" s="18" t="inlineStr">
+      <c r="BN20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BO20" s="18" t="inlineStr">
+      <c r="BO20" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
@@ -14359,9 +14356,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -14369,9 +14366,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -14379,9 +14376,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="K25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -14389,9 +14386,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="M25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -14399,9 +14396,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="O25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="O25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="P25" s="22" t="inlineStr">
@@ -14409,9 +14406,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="Q25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="Q25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="R25" s="22" t="inlineStr">
@@ -14419,9 +14416,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="S25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="S25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="T25" s="22" t="inlineStr">
@@ -14589,9 +14586,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB25" s="22" t="inlineStr">
@@ -14599,9 +14596,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD25" s="22" t="inlineStr">
@@ -14609,9 +14606,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF25" s="22" t="inlineStr">
@@ -14619,9 +14616,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH25" s="22" t="inlineStr">
@@ -14629,9 +14626,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ25" s="22" t="inlineStr">
@@ -14639,9 +14636,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL25" s="22" t="inlineStr">
@@ -14649,9 +14646,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN25" s="22" t="inlineStr">
@@ -14659,9 +14656,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO25" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO25" s="22" t="inlineStr">
+        <is>
+          <t>30/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -15929,9 +15926,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA29" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA29" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB29" s="22" t="inlineStr">
@@ -15939,9 +15936,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC29" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC29" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD29" s="22" t="inlineStr">
@@ -15949,9 +15946,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE29" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE29" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF29" s="22" t="inlineStr">
@@ -15959,9 +15956,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG29" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG29" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH29" s="22" t="inlineStr">
@@ -15969,9 +15966,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI29" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI29" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ29" s="22" t="inlineStr">
@@ -15979,9 +15976,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK29" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK29" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL29" s="22" t="inlineStr">
@@ -15989,9 +15986,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM29" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM29" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN29" s="22" t="inlineStr">
@@ -15999,9 +15996,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO29" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO29" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -16104,9 +16101,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="U30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="U30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="V30" s="22" t="inlineStr">
@@ -16114,9 +16111,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="W30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="W30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="X30" s="22" t="inlineStr">
@@ -16124,9 +16121,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="Y30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="Y30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="Z30" s="22" t="inlineStr">
@@ -16134,9 +16131,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AA30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AA30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AB30" s="22" t="inlineStr">
@@ -16144,9 +16141,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AC30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AC30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AD30" s="22" t="inlineStr">
@@ -16154,9 +16151,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AE30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AE30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AF30" s="22" t="inlineStr">
@@ -16164,9 +16161,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AG30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AG30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AH30" s="22" t="inlineStr">
@@ -16174,9 +16171,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AI30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AI30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AJ30" s="22" t="inlineStr">
@@ -16184,9 +16181,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AK30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AK30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AL30" s="22" t="inlineStr">
@@ -16194,9 +16191,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AM30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AM30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AN30" s="22" t="inlineStr">
@@ -16204,9 +16201,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AO30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AO30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AP30" s="22" t="inlineStr">
@@ -16214,9 +16211,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AQ30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AQ30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AR30" s="22" t="inlineStr">
@@ -16224,9 +16221,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AS30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AS30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AT30" s="22" t="inlineStr">
@@ -16234,9 +16231,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AU30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AU30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AV30" s="22" t="inlineStr">
@@ -16244,9 +16241,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AW30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AW30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AX30" s="22" t="inlineStr">
@@ -16254,9 +16251,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AY30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AY30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AZ30" s="22" t="inlineStr">
@@ -16264,9 +16261,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB30" s="22" t="inlineStr">
@@ -16274,9 +16271,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD30" s="22" t="inlineStr">
@@ -16284,9 +16281,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF30" s="22" t="inlineStr">
@@ -16294,9 +16291,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH30" s="22" t="inlineStr">
@@ -16304,9 +16301,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ30" s="22" t="inlineStr">
@@ -16314,9 +16311,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL30" s="22" t="inlineStr">
@@ -16324,9 +16321,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN30" s="22" t="inlineStr">
@@ -16334,9 +16331,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO30" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO30" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -16599,9 +16596,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA31" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA31" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB31" s="22" t="inlineStr">
@@ -16609,9 +16606,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC31" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC31" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD31" s="22" t="inlineStr">
@@ -16619,9 +16616,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE31" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE31" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF31" s="22" t="inlineStr">
@@ -16629,9 +16626,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG31" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG31" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH31" s="22" t="inlineStr">
@@ -16639,9 +16636,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI31" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI31" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ31" s="22" t="inlineStr">
@@ -16649,9 +16646,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK31" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK31" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL31" s="22" t="inlineStr">
@@ -16659,9 +16656,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM31" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM31" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN31" s="22" t="inlineStr">
@@ -16669,9 +16666,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO31" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO31" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -16934,9 +16931,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA32" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA32" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB32" s="22" t="inlineStr">
@@ -16944,9 +16941,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC32" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC32" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD32" s="22" t="inlineStr">
@@ -16954,9 +16951,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE32" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE32" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF32" s="22" t="inlineStr">
@@ -16964,9 +16961,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG32" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG32" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH32" s="22" t="inlineStr">
@@ -16974,9 +16971,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI32" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI32" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ32" s="22" t="inlineStr">
@@ -16984,9 +16981,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK32" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK32" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL32" s="22" t="inlineStr">
@@ -16994,9 +16991,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM32" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM32" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN32" s="22" t="inlineStr">
@@ -17004,9 +17001,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO32" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO32" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -17269,9 +17266,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA33" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA33" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB33" s="22" t="inlineStr">
@@ -17279,9 +17276,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC33" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC33" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD33" s="22" t="inlineStr">
@@ -17289,9 +17286,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE33" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE33" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF33" s="22" t="inlineStr">
@@ -17299,9 +17296,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG33" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG33" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH33" s="22" t="inlineStr">
@@ -17309,9 +17306,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI33" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI33" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ33" s="22" t="inlineStr">
@@ -17319,9 +17316,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK33" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK33" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL33" s="22" t="inlineStr">
@@ -17329,9 +17326,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM33" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM33" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN33" s="22" t="inlineStr">
@@ -17339,9 +17336,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO33" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO33" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -17604,9 +17601,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA34" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA34" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB34" s="22" t="inlineStr">
@@ -17614,9 +17611,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC34" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC34" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD34" s="22" t="inlineStr">
@@ -17624,9 +17621,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE34" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE34" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF34" s="22" t="inlineStr">
@@ -17634,9 +17631,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG34" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG34" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH34" s="22" t="inlineStr">
@@ -17644,9 +17641,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI34" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI34" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ34" s="22" t="inlineStr">
@@ -17654,9 +17651,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK34" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK34" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL34" s="22" t="inlineStr">
@@ -17664,9 +17661,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM34" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM34" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN34" s="22" t="inlineStr">
@@ -17674,9 +17671,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO34" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO34" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -17779,9 +17776,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="U35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="U35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="V35" s="22" t="inlineStr">
@@ -17789,9 +17786,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="W35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="W35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="X35" s="22" t="inlineStr">
@@ -17799,9 +17796,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="Y35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="Y35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="Z35" s="22" t="inlineStr">
@@ -17809,9 +17806,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AA35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AA35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AB35" s="22" t="inlineStr">
@@ -17819,9 +17816,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AC35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AC35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AD35" s="22" t="inlineStr">
@@ -17829,9 +17826,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AE35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AE35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AF35" s="22" t="inlineStr">
@@ -17839,9 +17836,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AG35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AG35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AH35" s="22" t="inlineStr">
@@ -17849,9 +17846,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AI35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AI35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AJ35" s="22" t="inlineStr">
@@ -17859,9 +17856,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AK35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AK35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AL35" s="22" t="inlineStr">
@@ -17869,9 +17866,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AM35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AM35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AN35" s="22" t="inlineStr">
@@ -17879,9 +17876,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AO35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AO35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AP35" s="22" t="inlineStr">
@@ -17889,9 +17886,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AQ35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AQ35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AR35" s="22" t="inlineStr">
@@ -17899,9 +17896,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AS35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AS35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AT35" s="22" t="inlineStr">
@@ -17909,9 +17906,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AU35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AU35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AV35" s="22" t="inlineStr">
@@ -17919,9 +17916,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AW35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AW35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AX35" s="22" t="inlineStr">
@@ -17929,9 +17926,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AY35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AY35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AZ35" s="22" t="inlineStr">
@@ -17939,9 +17936,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB35" s="22" t="inlineStr">
@@ -17949,9 +17946,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD35" s="22" t="inlineStr">
@@ -17959,9 +17956,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF35" s="22" t="inlineStr">
@@ -17969,9 +17966,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH35" s="22" t="inlineStr">
@@ -17979,9 +17976,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ35" s="22" t="inlineStr">
@@ -17989,9 +17986,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL35" s="22" t="inlineStr">
@@ -17999,9 +17996,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN35" s="22" t="inlineStr">
@@ -18009,9 +18006,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO35" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO35" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -18114,9 +18111,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="U36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="U36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="V36" s="22" t="inlineStr">
@@ -18124,9 +18121,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="W36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="W36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="X36" s="22" t="inlineStr">
@@ -18134,9 +18131,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="Y36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="Y36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="Z36" s="22" t="inlineStr">
@@ -18144,9 +18141,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AA36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AA36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AB36" s="22" t="inlineStr">
@@ -18154,9 +18151,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AC36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AC36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AD36" s="22" t="inlineStr">
@@ -18164,9 +18161,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AE36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AE36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AF36" s="22" t="inlineStr">
@@ -18174,9 +18171,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AG36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AG36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AH36" s="22" t="inlineStr">
@@ -18184,9 +18181,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AI36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AI36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AJ36" s="22" t="inlineStr">
@@ -18194,9 +18191,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AK36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AK36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AL36" s="22" t="inlineStr">
@@ -18204,9 +18201,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AM36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AM36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AN36" s="22" t="inlineStr">
@@ -18214,9 +18211,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AO36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AO36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AP36" s="22" t="inlineStr">
@@ -18224,9 +18221,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AQ36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AQ36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AR36" s="22" t="inlineStr">
@@ -18234,9 +18231,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AS36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AS36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AT36" s="22" t="inlineStr">
@@ -18244,9 +18241,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AU36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AU36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AV36" s="22" t="inlineStr">
@@ -18254,9 +18251,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AW36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AW36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AX36" s="22" t="inlineStr">
@@ -18264,9 +18261,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="AY36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="AY36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="AZ36" s="22" t="inlineStr">
@@ -18274,9 +18271,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB36" s="22" t="inlineStr">
@@ -18284,9 +18281,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD36" s="22" t="inlineStr">
@@ -18294,9 +18291,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF36" s="22" t="inlineStr">
@@ -18304,9 +18301,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH36" s="22" t="inlineStr">
@@ -18314,9 +18311,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ36" s="22" t="inlineStr">
@@ -18324,9 +18321,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL36" s="22" t="inlineStr">
@@ -18334,9 +18331,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN36" s="22" t="inlineStr">
@@ -18344,9 +18341,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO36" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO36" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -18609,9 +18606,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BA37" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BA37" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BB37" s="22" t="inlineStr">
@@ -18619,9 +18616,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BC37" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BC37" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BD37" s="22" t="inlineStr">
@@ -18629,9 +18626,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BE37" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BE37" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BF37" s="22" t="inlineStr">
@@ -18639,9 +18636,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BG37" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BG37" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BH37" s="22" t="inlineStr">
@@ -18649,9 +18646,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BI37" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BI37" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ37" s="22" t="inlineStr">
@@ -18659,9 +18656,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BK37" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BK37" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BL37" s="22" t="inlineStr">
@@ -18669,9 +18666,9 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="BM37" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BM37" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
       <c r="BN37" s="22" t="inlineStr">
@@ -18679,9 +18676,9 @@
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="BO37" s="23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="BO37" s="22" t="inlineStr">
+        <is>
+          <t>20/08/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -18709,312 +18706,312 @@
           <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
         </is>
       </c>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="G38" s="18" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="H38" s="18" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="J38" s="18" t="inlineStr">
+      <c r="J38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="K38" s="18" t="inlineStr">
+      <c r="K38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="L38" s="18" t="inlineStr">
+      <c r="L38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="M38" s="18" t="inlineStr">
+      <c r="M38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="N38" s="18" t="inlineStr">
+      <c r="N38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="O38" s="18" t="inlineStr">
+      <c r="O38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="P38" s="18" t="inlineStr">
+      <c r="P38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="Q38" s="18" t="inlineStr">
+      <c r="Q38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="R38" s="18" t="inlineStr">
+      <c r="R38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="S38" s="18" t="inlineStr">
+      <c r="S38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="T38" s="18" t="inlineStr">
+      <c r="T38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="U38" s="18" t="inlineStr">
+      <c r="U38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="V38" s="18" t="inlineStr">
+      <c r="V38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="W38" s="18" t="inlineStr">
+      <c r="W38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="X38" s="18" t="inlineStr">
+      <c r="X38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="Y38" s="18" t="inlineStr">
+      <c r="Y38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="Z38" s="18" t="inlineStr">
+      <c r="Z38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AA38" s="18" t="inlineStr">
+      <c r="AA38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AB38" s="18" t="inlineStr">
+      <c r="AB38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AC38" s="18" t="inlineStr">
+      <c r="AC38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AD38" s="18" t="inlineStr">
+      <c r="AD38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AE38" s="18" t="inlineStr">
+      <c r="AE38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AF38" s="18" t="inlineStr">
+      <c r="AF38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AG38" s="18" t="inlineStr">
+      <c r="AG38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AH38" s="18" t="inlineStr">
+      <c r="AH38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AI38" s="18" t="inlineStr">
+      <c r="AI38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AJ38" s="18" t="inlineStr">
+      <c r="AJ38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AK38" s="18" t="inlineStr">
+      <c r="AK38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AL38" s="18" t="inlineStr">
+      <c r="AL38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AM38" s="18" t="inlineStr">
+      <c r="AM38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AN38" s="18" t="inlineStr">
+      <c r="AN38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AO38" s="18" t="inlineStr">
+      <c r="AO38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AP38" s="18" t="inlineStr">
+      <c r="AP38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AQ38" s="18" t="inlineStr">
+      <c r="AQ38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AR38" s="18" t="inlineStr">
+      <c r="AR38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AS38" s="18" t="inlineStr">
+      <c r="AS38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AT38" s="18" t="inlineStr">
+      <c r="AT38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AU38" s="18" t="inlineStr">
+      <c r="AU38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AV38" s="18" t="inlineStr">
+      <c r="AV38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AW38" s="18" t="inlineStr">
+      <c r="AW38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AX38" s="18" t="inlineStr">
+      <c r="AX38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AY38" s="18" t="inlineStr">
+      <c r="AY38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="AZ38" s="18" t="inlineStr">
+      <c r="AZ38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BA38" s="18" t="inlineStr">
+      <c r="BA38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BB38" s="18" t="inlineStr">
+      <c r="BB38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BC38" s="18" t="inlineStr">
+      <c r="BC38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BD38" s="18" t="inlineStr">
+      <c r="BD38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BE38" s="18" t="inlineStr">
+      <c r="BE38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BF38" s="18" t="inlineStr">
+      <c r="BF38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BG38" s="18" t="inlineStr">
+      <c r="BG38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BH38" s="18" t="inlineStr">
+      <c r="BH38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BI38" s="18" t="inlineStr">
+      <c r="BI38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BJ38" s="18" t="inlineStr">
+      <c r="BJ38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BK38" s="18" t="inlineStr">
+      <c r="BK38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BL38" s="18" t="inlineStr">
+      <c r="BL38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BM38" s="18" t="inlineStr">
+      <c r="BM38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BN38" s="18" t="inlineStr">
+      <c r="BN38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
       </c>
-      <c r="BO38" s="18" t="inlineStr">
+      <c r="BO38" s="22" t="inlineStr">
         <is>
           <t>LICENCIA MÉDICA</t>
         </is>
@@ -21873,7 +21870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21995,14 +21992,14 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I5" s="18" t="inlineStr">
@@ -22020,7 +22017,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22055,14 +22052,14 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr">
@@ -22080,7 +22077,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22115,14 +22112,14 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I7" s="18" t="inlineStr">
@@ -22140,7 +22137,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22175,14 +22172,14 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -22200,7 +22197,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22235,14 +22232,14 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -22260,7 +22257,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L9" s="25" t="inlineStr">
+      <c r="L9" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22295,14 +22292,14 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
@@ -22320,7 +22317,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L10" s="25" t="inlineStr">
+      <c r="L10" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22355,14 +22352,14 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
@@ -22380,7 +22377,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L11" s="25" t="inlineStr">
+      <c r="L11" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22415,14 +22412,14 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
@@ -22440,7 +22437,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22475,14 +22472,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
@@ -22500,7 +22497,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22535,14 +22532,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -22560,7 +22557,7 @@
           <t>A su reincorporación (licencia médica)</t>
         </is>
       </c>
-      <c r="L14" s="25" t="inlineStr">
+      <c r="L14" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22595,14 +22592,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I15" s="18" t="inlineStr">
@@ -22620,7 +22617,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L15" s="25" t="inlineStr">
+      <c r="L15" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22655,14 +22652,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I16" s="18" t="inlineStr">
@@ -22680,7 +22677,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L16" s="25" t="inlineStr">
+      <c r="L16" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22715,14 +22712,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I17" s="18" t="inlineStr">
@@ -22740,7 +22737,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L17" s="25" t="inlineStr">
+      <c r="L17" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22775,14 +22772,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -22800,7 +22797,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L18" s="25" t="inlineStr">
+      <c r="L18" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22835,14 +22832,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I19" s="18" t="inlineStr">
@@ -22860,7 +22857,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
+      <c r="L19" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22895,14 +22892,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I20" s="18" t="inlineStr">
@@ -22920,7 +22917,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L20" s="25" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -22955,14 +22952,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I21" s="18" t="inlineStr">
@@ -22980,7 +22977,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L21" s="25" t="inlineStr">
+      <c r="L21" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23015,14 +23012,14 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I22" s="18" t="inlineStr">
@@ -23040,7 +23037,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L22" s="25" t="inlineStr">
+      <c r="L22" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23075,14 +23072,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I23" s="18" t="inlineStr">
@@ -23100,7 +23097,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
+      <c r="L23" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23135,14 +23132,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -23160,7 +23157,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L24" s="25" t="inlineStr">
+      <c r="L24" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23195,14 +23192,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G25" s="24" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
@@ -23220,7 +23217,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L25" s="25" t="inlineStr">
+      <c r="L25" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23255,14 +23252,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G26" s="24" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
@@ -23280,7 +23277,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
+      <c r="L26" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23315,14 +23312,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G27" s="24" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
@@ -23340,7 +23337,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
+      <c r="L27" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23375,14 +23372,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I28" s="18" t="inlineStr">
@@ -23400,7 +23397,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L28" s="25" t="inlineStr">
+      <c r="L28" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23435,14 +23432,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G29" s="24" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
@@ -23460,7 +23457,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L29" s="25" t="inlineStr">
+      <c r="L29" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23495,14 +23492,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
@@ -23520,7 +23517,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L30" s="25" t="inlineStr">
+      <c r="L30" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23555,14 +23552,14 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="G31" s="24" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr">
@@ -23580,7 +23577,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L31" s="25" t="inlineStr">
+      <c r="L31" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23615,14 +23612,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G32" s="24" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I32" s="18" t="inlineStr">
@@ -23640,7 +23637,7 @@
           <t>A su reincorporación (licencia médica)</t>
         </is>
       </c>
-      <c r="L32" s="25" t="inlineStr">
+      <c r="L32" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23675,14 +23672,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G33" s="24" t="inlineStr">
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
@@ -23700,7 +23697,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L33" s="25" t="inlineStr">
+      <c r="L33" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23735,14 +23732,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G34" s="24" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I34" s="18" t="inlineStr">
@@ -23760,7 +23757,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L34" s="25" t="inlineStr">
+      <c r="L34" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23795,14 +23792,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G35" s="24" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
@@ -23820,7 +23817,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L35" s="25" t="inlineStr">
+      <c r="L35" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23855,14 +23852,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G36" s="24" t="inlineStr">
+      <c r="G36" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
@@ -23880,7 +23877,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L36" s="25" t="inlineStr">
+      <c r="L36" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23915,14 +23912,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G37" s="24" t="inlineStr">
+      <c r="G37" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I37" s="18" t="inlineStr">
@@ -23940,7 +23937,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L37" s="25" t="inlineStr">
+      <c r="L37" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -23975,14 +23972,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G38" s="24" t="inlineStr">
+      <c r="G38" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
@@ -24000,7 +23997,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L38" s="25" t="inlineStr">
+      <c r="L38" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24035,14 +24032,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G39" s="24" t="inlineStr">
+      <c r="G39" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr">
@@ -24060,7 +24057,7 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L39" s="25" t="inlineStr">
+      <c r="L39" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
@@ -24095,14 +24092,14 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="G40" s="24" t="inlineStr">
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>Difusión y Evaluación</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>Plan de Gestión de Riesgos de Desastres</t>
+          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
@@ -24120,2223 +24117,63 @@
           <t>28/09/2026 al 09/10/2026</t>
         </is>
       </c>
-      <c r="L40" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>15338787-7</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>ALBERTO REBOLLEDO</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>Supervisor de Operaciones</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H41" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I41" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K41" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L41" s="25" t="inlineStr">
+      <c r="L40" s="24" t="inlineStr">
         <is>
           <t>POR CONFIRMAR</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>15612089-8</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>PEDRO LUIS ALVAREZ PEREZ</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>Controlador Operación Puerto</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H42" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I42" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K42" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L42" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>NOTAS A LA PLANILLA 3</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>11326446-2</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>ROBERTO ENRIQUE FRITIS ZALAZAR</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>Operador Líder Puerto</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H43" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I43" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K43" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L43" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Difusión comprometida: 21/09/2026 al 25/09/2026.  Evaluación comprometida: 28/09/2026 al 09/10/2026.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>11439946-9</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>HERNAN GUSTAVO DONOSO BORQUEZ</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H44" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I44" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K44" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L44" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>El código único del documento está POR CONFIRMAR: debe asignarse dentro de la numeración del proceso 3.8 antes de subir la planilla a SIMIN OL.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>16602101-4</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>ALEJANDRO ANDRES HERRERA AGUILERA</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H45" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I45" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K45" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L45" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>El responsable de ejecución está POR CONFIRMAR para cada turno.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>17606185-5</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>JULIO ELIAS HIDALGO GARCIA</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H46" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I46" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K46" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L46" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>Se incluye la columna "Turno" (G1 a G4) porque la difusión debe coordinarse por turno dentro de la semana comprometida. No forma parte del formato original de la planilla.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>20502538-3</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>LISSETTE CONSUELO CALDERÓN GALLARDO</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>Operador Avanzado Puerto</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G47" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H47" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I47" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L47" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>Los trabajadores con licencia médica llevan como fecha comprometida "A su reincorporación": CRISTOPHER NICOLA SANTIBAÑEZ BAHAMONDES, LEONARDO SAAVEDRA.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>18403704-1</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>CRISTIAN OMAR TAPIA LOBOS</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>Operador Avanzado Puerto</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H48" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K48" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L48" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>Documento 3.8.3.12 "Procedimiento de Emergencia": corresponde al "Plan de Respuesta a Emergencia Local Valle Copiapó — Puerto Punta Totoralillo", aprobado el 25/02/2025. Por esa razón el "Plan de Gestión de Riesgos de Desastres" no se incorpora a este programa: es el mismo documento, ya difundido y evaluado, y figura en las Planillas 1 y 2.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>13515438-5</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>RICARDO KUNZ FLORES</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>Supervisor de Operaciones</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H49" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K49" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L49" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>15070549-5</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>CRISTOPHER NICOLA SANTIBAÑEZ BAHAMONDES</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>Controlador Operación Puerto</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H50" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I50" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J50" s="18" t="inlineStr">
-        <is>
-          <t>A su reincorporación (licencia médica)</t>
-        </is>
-      </c>
-      <c r="K50" s="18" t="inlineStr">
-        <is>
-          <t>A su reincorporación (licencia médica)</t>
-        </is>
-      </c>
-      <c r="L50" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>11748137-9</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>ELIAS BALDOMERO BUSTAMANTE ROJAS</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>Operador Líder Puerto</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H51" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I51" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K51" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L51" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>17302695-1</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>MAURICIO ANDRES BARAHONA CASTILLO</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H52" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I52" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K52" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L52" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>15633680-7</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>CRISTOBAL FELIPE DE LA FUENTE CISTERNA</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H53" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I53" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L53" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>11724812-7</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>CRISTIAN HOMERO DIAZ VEGA</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H54" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I54" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K54" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L54" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>19352719-1</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>MATIAS IGNACIO FUENTES FUENTES</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G55" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H55" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I55" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K55" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L55" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>16821701-3</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>VICTOR ALEJANDRO JOFRE DELGADO</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G56" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H56" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I56" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K56" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L56" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>17302213-1</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>MARCO ANDRE OVIEDO FERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H57" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I57" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J57" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K57" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L57" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>15913813-5</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>JOSE ROBERTO VALDES ROJAS</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="G58" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H58" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I58" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J58" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K58" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L58" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>15014074-9</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>MIGUEL ANGEL MARTINEZ VEGA</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>Supervisor de Operaciones</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G59" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H59" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I59" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J59" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K59" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L59" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>18211987-3</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>OSVALDO IGNACIO MUÑOZ BARRIA</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>Controlador Operación Puerto</t>
-        </is>
-      </c>
-      <c r="E60" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G60" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H60" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I60" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J60" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K60" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L60" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>14114592-4</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>JUAN ALEJANDRO IBACETA GARCIA</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>Operador Líder Puerto</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G61" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H61" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I61" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J61" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K61" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L61" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>15033441-1</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>DARIO ANTONIO CASTILLO OLGUIN</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E62" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G62" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H62" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I62" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J62" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K62" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L62" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>19124925-9</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>LUIS FELIPE CISTERNAS AGUIRRE</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E63" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G63" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H63" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I63" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J63" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K63" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L63" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>17294689-5</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>RODRIGO EDUARDO COLLAO LABARCA</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G64" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H64" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I64" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K64" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L64" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>12444781-K</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>ROBERTO MAURICIO ESCOBAR RUBINA</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E65" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G65" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H65" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I65" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J65" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K65" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L65" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="16" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>14151103-3</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>JORGE ANGELO VEGA HERRERA</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G66" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H66" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I66" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J66" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K66" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L66" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="16" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
-        <is>
-          <t>21870635-5</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>RODRIGO DAZA BERTICHEVIC</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>Operador Base</t>
-        </is>
-      </c>
-      <c r="E67" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="G67" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H67" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I67" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J67" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K67" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L67" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>LEONARDO SAAVEDRA</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>Supervisor de Operaciones</t>
-        </is>
-      </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G68" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H68" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I68" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J68" s="18" t="inlineStr">
-        <is>
-          <t>A su reincorporación (licencia médica)</t>
-        </is>
-      </c>
-      <c r="K68" s="18" t="inlineStr">
-        <is>
-          <t>A su reincorporación (licencia médica)</t>
-        </is>
-      </c>
-      <c r="L68" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>15870483-8</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>JAMES JHON JAN-SIN BOWN HERRERA</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>Controlador Operación Puerto</t>
-        </is>
-      </c>
-      <c r="E69" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G69" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H69" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I69" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J69" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K69" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L69" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="16" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>13358835-3</t>
-        </is>
-      </c>
-      <c r="C70" s="17" t="inlineStr">
-        <is>
-          <t>OSVALDO ARTURO GALLEGUILLOS ARAYA</t>
-        </is>
-      </c>
-      <c r="D70" s="17" t="inlineStr">
-        <is>
-          <t>Operador Líder Puerto</t>
-        </is>
-      </c>
-      <c r="E70" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F70" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G70" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H70" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I70" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J70" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K70" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L70" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>18138905-2</t>
-        </is>
-      </c>
-      <c r="C71" s="17" t="inlineStr">
-        <is>
-          <t>ALEX NICOLAS BARAHONA CASTILLO</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E71" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G71" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H71" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I71" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J71" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K71" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L71" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>15031548-4</t>
-        </is>
-      </c>
-      <c r="C72" s="17" t="inlineStr">
-        <is>
-          <t>JULIO ANDRES BARLARO PODETTI</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E72" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G72" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H72" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I72" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J72" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K72" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L72" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>17902171-4</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <t>FERNANDO ILDEFONSO VARGAS ROMO</t>
-        </is>
-      </c>
-      <c r="D73" s="17" t="inlineStr">
-        <is>
-          <t>Operador Especialista Puerto</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G73" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H73" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I73" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J73" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K73" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L73" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>18399063-2</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>JEAN MARIO CARVAJAL SALINAS</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="inlineStr">
-        <is>
-          <t>Operador Avanzado Puerto</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G74" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H74" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I74" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J74" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K74" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L74" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>18845157-8</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <t>ESTEBAN GERMAN TAPIA LOBOS</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>Operador Avanzado Puerto</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F75" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G75" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H75" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I75" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J75" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K75" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L75" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="16" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>19353026-5</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
-        <is>
-          <t>GABRIELA VARAS</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="inlineStr">
-        <is>
-          <t>Operador Base</t>
-        </is>
-      </c>
-      <c r="E76" s="17" t="inlineStr">
-        <is>
-          <t>COMPAÑÍA MINERA DEL PACIFICO [CMP]</t>
-        </is>
-      </c>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="G76" s="24" t="inlineStr">
-        <is>
-          <t>Difusión y Evaluación</t>
-        </is>
-      </c>
-      <c r="H76" s="17" t="inlineStr">
-        <is>
-          <t>Instructivo Llenado de VAT (Verificación y Autorización de Trabajo)</t>
-        </is>
-      </c>
-      <c r="I76" s="18" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-      <c r="J76" s="16" t="inlineStr">
-        <is>
-          <t>21/09/2026 al 25/09/2026</t>
-        </is>
-      </c>
-      <c r="K76" s="16" t="inlineStr">
-        <is>
-          <t>28/09/2026 al 09/10/2026</t>
-        </is>
-      </c>
-      <c r="L76" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>NOTAS A LA PLANILLA 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="26" t="inlineStr">
-        <is>
-          <t>Difusión comprometida: 21/09/2026 al 25/09/2026.  Evaluación comprometida: 28/09/2026 al 09/10/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>Los códigos únicos de ambos documentos están POR CONFIRMAR: deben asignarse dentro de la numeración del proceso 3.8 antes de subir la planilla a SIMIN OL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="26" t="inlineStr">
-        <is>
-          <t>El responsable de ejecución está POR CONFIRMAR para cada turno.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="26" t="inlineStr">
-        <is>
-          <t>Se incluye la columna "Turno" (G1 a G4) porque la difusión debe coordinarse por turno dentro de la semana comprometida. No forma parte del formato original de la planilla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="26" t="inlineStr">
-        <is>
-          <t>Los trabajadores con licencia médica llevan como fecha comprometida "A su reincorporación": CRISTOPHER NICOLA SANTIBAÑEZ BAHAMONDES, LEONARDO SAAVEDRA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="26" t="inlineStr">
-        <is>
-          <t>Documento 3.8.3.12 "Procedimiento de Emergencia": corresponde al "Plan de Respuesta a Emergencia Local Valle Copiapó — Puerto Punta Totoralillo", aprobado el 25/02/2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="27" t="inlineStr">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>Trabajadores con RUT POR CONFIRMAR: LEONARDO SAAVEDRA.</t>
         </is>
